--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
@@ -5222,7 +5222,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
@@ -5222,7 +5222,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
@@ -5222,7 +5222,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20250929_235335.xlsx
@@ -5222,7 +5222,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
